--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487147_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487147_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6669</v>
+        <v>11.2013</v>
       </c>
       <c r="E2" t="n">
-        <v>10.0135</v>
+        <v>10.1731</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6534</v>
+        <v>1.0282</v>
       </c>
       <c r="G2" t="n">
         <v>10.1728</v>
@@ -610,13 +610,13 @@
         <v>1.158</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2247</v>
+        <v>0.3097</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5208</v>
+        <v>-0.3612</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2961</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>2.4559</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4865</v>
+        <v>6.546</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0326</v>
+        <v>4.0921</v>
       </c>
       <c r="F3" t="n">
         <v>2.454</v>
@@ -688,10 +688,10 @@
         <v>1.158</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4422</v>
+        <v>1.5017</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1468</v>
+        <v>0.2062</v>
       </c>
       <c r="U3" t="n">
         <v>1.2955</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9159</v>
+        <v>5.7091</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6588</v>
+        <v>4.4787</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2571</v>
+        <v>1.2303</v>
       </c>
       <c r="G4" t="n">
         <v>6.0528</v>
@@ -766,13 +766,13 @@
         <v>1.158</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0284</v>
+        <v>0.8216</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9518</v>
+        <v>-0.1318</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9802</v>
+        <v>0.9534</v>
       </c>
       <c r="V4" t="n">
         <v>0.5717</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2845</v>
+        <v>3.4358</v>
       </c>
       <c r="E5" t="n">
-        <v>4.722</v>
+        <v>3.9804</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4375</v>
+        <v>-0.5446</v>
       </c>
       <c r="G5" t="n">
         <v>3.4796</v>
@@ -844,13 +844,13 @@
         <v>0.579</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7048</v>
+        <v>1.856</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5269</v>
+        <v>0.7853</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1779</v>
+        <v>1.0708</v>
       </c>
       <c r="V5" t="n">
         <v>-1.5138</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6636</v>
+        <v>2.0221</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8698</v>
+        <v>4.2283</v>
       </c>
       <c r="F6" t="n">
         <v>-2.2062</v>
@@ -922,10 +922,10 @@
         <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7516</v>
+        <v>1.1101</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9333</v>
+        <v>0.2918</v>
       </c>
       <c r="U6" t="n">
         <v>0.8183</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6895</v>
+        <v>0.863</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0828</v>
+        <v>0.2831</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6067</v>
+        <v>0.5799</v>
       </c>
       <c r="G7" t="n">
         <v>0.4099</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2796</v>
+        <v>0.4531</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.2003</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2796</v>
+        <v>0.2528</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1793</v>
+        <v>0.794</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8988</v>
+        <v>-0.4982</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0781</v>
+        <v>1.2922</v>
       </c>
       <c r="G8" t="n">
         <v>0.1816</v>
@@ -1078,13 +1078,13 @@
         <v>0.772</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.5195</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4614</v>
+        <v>-0.0608</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3662</v>
+        <v>0.5803</v>
       </c>
       <c r="V8" t="n">
         <v>0.2859</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1215</v>
+        <v>0.2018</v>
       </c>
       <c r="E9" t="n">
         <v>0.0814</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0401</v>
+        <v>0.1204</v>
       </c>
       <c r="G9" t="n">
         <v>0.2015</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.08</v>
+        <v>0.0003</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.08</v>
+        <v>0.0003</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3933</v>
+        <v>-1.3546</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4735</v>
+        <v>-0.3545</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9198</v>
+        <v>-1.0001</v>
       </c>
       <c r="G10" t="n">
         <v>0.0059</v>
@@ -1234,13 +1234,13 @@
         <v>0.772</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0218</v>
+        <v>0.0605</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5354</v>
+        <v>-0.4164</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5572</v>
+        <v>0.4769</v>
       </c>
       <c r="V10" t="n">
         <v>-1.228</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. SAINSBURY GARCIA</t>
+          <t>O. IBARROLA ITURRIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0819</v>
+        <v>-2.5145</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1277</v>
+        <v>-1.9327</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0458</v>
+        <v>-0.5819</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3051</v>
+        <v>0.7489</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0776</v>
+        <v>-0.5878</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3827</v>
+        <v>1.3366</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3186</v>
+        <v>0.8825</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8641</v>
+        <v>0.207</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5455</v>
+        <v>0.6755</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0135</v>
+        <v>-0.1336</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9417</v>
+        <v>-0.7948</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9282</v>
+        <v>0.6612</v>
       </c>
       <c r="P11" t="n">
+        <v>-2.3161</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-2.8951</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-3.8602</v>
-      </c>
       <c r="R11" t="n">
-        <v>0.965</v>
+        <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4079</v>
+        <v>1.1805</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7998</v>
+        <v>0.08</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6081</v>
+        <v>1.1005</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8999</v>
+        <v>-2.1278</v>
       </c>
       <c r="W11" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5138</v>
+        <v>-2.1278</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. IBARROLA ITURRIA</t>
+          <t>D. SAINSBURY GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9072</v>
+        <v>-2.6838</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.593</v>
+        <v>-2.5689</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3142</v>
+        <v>-0.1148</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7489</v>
+        <v>0.3051</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5878</v>
+        <v>-0.0776</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3366</v>
+        <v>0.3827</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8825</v>
+        <v>0.3186</v>
       </c>
       <c r="K12" t="n">
-        <v>0.207</v>
+        <v>0.8641</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6755</v>
+        <v>-0.5455</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1336</v>
+        <v>-0.0135</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7948</v>
+        <v>-0.9417</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6612</v>
+        <v>0.9282</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.3161</v>
+        <v>-2.8951</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.8951</v>
+        <v>-3.8602</v>
       </c>
       <c r="R12" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7879</v>
+        <v>0.8061</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5803</v>
+        <v>0.3586</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3682</v>
+        <v>0.4475</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1278</v>
+        <v>-0.8999</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1278</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>23.6253</v>
+        <v>24.22019999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>21.3679</v>
+        <v>21.9628</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2575</v>
+        <v>2.257400000000001</v>
       </c>
       <c r="G13" t="n">
         <v>26.4335</v>
@@ -1468,13 +1468,13 @@
         <v>7.72</v>
       </c>
       <c r="S13" t="n">
-        <v>8.0243</v>
+        <v>8.619100000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3571</v>
+        <v>0.952</v>
       </c>
       <c r="U13" t="n">
-        <v>7.667300000000001</v>
+        <v>7.6672</v>
       </c>
       <c r="V13" t="n">
         <v>-3.1122</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5481</v>
+        <v>1.6807</v>
       </c>
       <c r="E14" t="n">
-        <v>2.106</v>
+        <v>2.5066</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5579</v>
+        <v>-0.8259</v>
       </c>
       <c r="G14" t="n">
         <v>-1.878</v>
@@ -1546,13 +1546,13 @@
         <v>2.1231</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8904</v>
+        <v>-0.7578</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4277</v>
+        <v>-1.0271</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5373</v>
+        <v>0.2693</v>
       </c>
       <c r="V14" t="n">
         <v>2.1934</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6161</v>
+        <v>0.8164</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3404</v>
+        <v>1.5407</v>
       </c>
       <c r="F16" t="n">
         <v>-0.7243000000000001</v>
@@ -1702,10 +1702,10 @@
         <v>0.579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3265</v>
+        <v>-0.1262</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3569</v>
+        <v>-0.1566</v>
       </c>
       <c r="U16" t="n">
         <v>0.0304</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8857</v>
+        <v>-1.1058</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6454</v>
+        <v>0.345</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5311</v>
+        <v>-1.4508</v>
       </c>
       <c r="G17" t="n">
         <v>-1.7753</v>
@@ -1780,13 +1780,13 @@
         <v>0.965</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6894</v>
+        <v>-0.9095</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4627</v>
+        <v>-0.7631</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2267</v>
+        <v>-0.1464</v>
       </c>
       <c r="V17" t="n">
         <v>0.614</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9002</v>
+        <v>-1.3344</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6978</v>
+        <v>2.3974</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.598</v>
+        <v>-3.7318</v>
       </c>
       <c r="G18" t="n">
         <v>0.6287</v>
@@ -1858,13 +1858,13 @@
         <v>0.579</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1778</v>
+        <v>-0.6121</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1057</v>
+        <v>-0.4062</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0721</v>
+        <v>-0.2059</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. ECHEONDO LACALLE</t>
+          <t>A. SAVITSKI SAVITSKAIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8216</v>
+        <v>-1.7261</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3101</v>
+        <v>-0.9369</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5116</v>
+        <v>-0.7891</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.24</v>
+        <v>-4.1701</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4668</v>
+        <v>-2.5628</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7733</v>
+        <v>-1.6072</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0614</v>
+        <v>-0.7794</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0207</v>
+        <v>-0.6731</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0407</v>
+        <v>-0.1064</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3014</v>
+        <v>-3.3906</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4875</v>
+        <v>-1.8898</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-1.5009</v>
       </c>
       <c r="P19" t="n">
-        <v>0.193</v>
+        <v>1.3511</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.193</v>
+        <v>-1.158</v>
       </c>
       <c r="R19" t="n">
-        <v>0.386</v>
+        <v>2.5091</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1606</v>
+        <v>-0.8146</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1785</v>
+        <v>-1.1273</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0178</v>
+        <v>0.3126</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.614</v>
+        <v>1.9076</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.1278</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.614</v>
+        <v>-0.2202</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SAVITSKI SAVITSKAIA</t>
+          <t>I. ECHEONDO LACALLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2136</v>
+        <v>-1.7949</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2373</v>
+        <v>-0.3101</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9762</v>
+        <v>-1.4848</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.1701</v>
+        <v>-1.24</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.5628</v>
+        <v>-0.4668</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6072</v>
+        <v>-0.7733</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7794</v>
+        <v>0.0614</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6731</v>
+        <v>0.0207</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1064</v>
+        <v>0.0407</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.3906</v>
+        <v>-1.3014</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8898</v>
+        <v>-0.4875</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5009</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3511</v>
+        <v>0.193</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.158</v>
+        <v>-0.193</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5091</v>
+        <v>0.386</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3021</v>
+        <v>-0.1338</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4277</v>
+        <v>-0.1785</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1256</v>
+        <v>0.0446</v>
       </c>
       <c r="V20" t="n">
-        <v>1.9076</v>
+        <v>-0.614</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1278</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2202</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.485</v>
+        <v>-3.1777</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8066</v>
+        <v>-1.6063</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6784</v>
+        <v>-1.5714</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4129</v>
@@ -2092,13 +2092,13 @@
         <v>0.386</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4931</v>
+        <v>-0.1857</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2974</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0427</v>
+        <v>-4.5567</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9986</v>
+        <v>-1.6996</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0442</v>
+        <v>-2.8571</v>
       </c>
       <c r="G22" t="n">
         <v>-7.0862</v>
@@ -2170,13 +2170,13 @@
         <v>2.7021</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.694</v>
+        <v>-1.2079</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5089</v>
+        <v>-1.2099</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1851</v>
+        <v>0.002</v>
       </c>
       <c r="V22" t="n">
         <v>2.1934</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6942</v>
+        <v>-5.2533</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8906</v>
+        <v>-3.6903</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8036</v>
+        <v>-1.563</v>
       </c>
       <c r="G23" t="n">
         <v>-4.1725</v>
@@ -2248,13 +2248,13 @@
         <v>1.7371</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4594</v>
+        <v>-1.0186</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1898</v>
+        <v>-0.9895</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2697</v>
+        <v>-0.0291</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8342000000000001</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.1427</v>
+        <v>-7.9021</v>
       </c>
       <c r="E24" t="n">
         <v>-4.926</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.2167</v>
+        <v>-2.9761</v>
       </c>
       <c r="G24" t="n">
         <v>-5.0023</v>
@@ -2326,13 +2326,13 @@
         <v>0.579</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3986</v>
+        <v>-1.158</v>
       </c>
       <c r="T24" t="n">
         <v>-0.8923</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5063</v>
+        <v>-0.2657</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1278</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-23.6254</v>
+        <v>-22.9578</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.257600000000001</v>
+        <v>-2.2575</v>
       </c>
       <c r="F25" t="n">
-        <v>-21.3679</v>
+        <v>-20.7002</v>
       </c>
       <c r="G25" t="n">
         <v>-26.4335</v>
@@ -2404,13 +2404,13 @@
         <v>15.4405</v>
       </c>
       <c r="S25" t="n">
-        <v>-8.0242</v>
+        <v>-7.3565</v>
       </c>
       <c r="T25" t="n">
-        <v>-7.667199999999999</v>
+        <v>-7.6673</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3572000000000001</v>
+        <v>0.3104999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>3.112099999999999</v>
